--- a/templates/negotiation-worksheets.xlsx
+++ b/templates/negotiation-worksheets.xlsx
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -97,8 +99,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -465,7 +467,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -605,6 +607,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -612,7 +615,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -726,6 +729,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -733,7 +737,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -828,5 +832,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>